--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-25.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T3"/>
+  <dimension ref="A1:T8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,15 +578,19 @@
       <c r="K2" t="n">
         <v>1.39</v>
       </c>
-      <c r="L2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>✅ LIQUIDADO</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -660,15 +664,19 @@
       <c r="K3" t="n">
         <v>1.62</v>
       </c>
-      <c r="L3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>✅ LIQUIDADO</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -692,6 +700,420 @@
       </c>
       <c r="T3" t="n">
         <v>39.79</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Czech 1 Liga</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Sparta Prague x Slovacko</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Sparta Prague</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Slovacko</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>AO Home Win</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>✅ LIQUIDADO</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>1031</v>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="R4" t="n">
+        <v>200</v>
+      </c>
+      <c r="S4" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="T4" t="n">
+        <v>32.93</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Belgian Pro League</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Club Brugge x Sint Truiden</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Club Brugge</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Sint Truiden</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>304</v>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="R5" t="n">
+        <v>200</v>
+      </c>
+      <c r="S5" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="T5" t="n">
+        <v>32.93</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Swedish Allsvenskan</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Mjallby x Hammarby</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Mjallby</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Hammarby</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lay Home/DC X2 (FavVis &lt;= 1.65)</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>8</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>1108</v>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="R6" t="n">
+        <v>200</v>
+      </c>
+      <c r="S6" t="n">
+        <v>28.57</v>
+      </c>
+      <c r="T6" t="n">
+        <v>27.28</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Dutch Eredivisie</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Sparta Rotterdam x Ajax</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Sparta Rotterdam</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Ajax</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lay Home/DC X2 (FavVis &lt;= 1.65)</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>1559</v>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="R7" t="n">
+        <v>200</v>
+      </c>
+      <c r="S7" t="n">
+        <v>38.46</v>
+      </c>
+      <c r="T7" t="n">
+        <v>36.73</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Greek Super League</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NFC Volos x Panathinaikos</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>NFC Volos</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Panathinaikos</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>2398</v>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="R8" t="n">
+        <v>200</v>
+      </c>
+      <c r="S8" t="n">
+        <v>37.04</v>
+      </c>
+      <c r="T8" t="n">
+        <v>35.37</v>
       </c>
     </row>
   </sheetData>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-25.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T8"/>
+  <dimension ref="A1:T14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -836,15 +836,19 @@
       <c r="K5" t="n">
         <v>1.31</v>
       </c>
-      <c r="L5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>3-2</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>✅ LIQUIDADO</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -918,15 +922,19 @@
       <c r="K6" t="n">
         <v>1.46</v>
       </c>
-      <c r="L6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>✅ LIQUIDADO</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1000,15 +1008,19 @@
       <c r="K7" t="n">
         <v>1.55</v>
       </c>
-      <c r="L7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>✅ LIQUIDADO</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1082,15 +1094,19 @@
       <c r="K8" t="n">
         <v>1.32</v>
       </c>
-      <c r="L8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>✅ LIQUIDADO</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1114,6 +1130,498 @@
       </c>
       <c r="T8" t="n">
         <v>35.37</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>German Bundesliga</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Freiburg x Bayern Munich</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Freiburg</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Bayern Munich</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lay Home/DC X2 (FavVis &lt;= 1.65)</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>3957</v>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="R9" t="n">
+        <v>200</v>
+      </c>
+      <c r="S9" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="T9" t="n">
+        <v>32.93</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Hungarian NB I</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Ferencvaros x MTK Budapest</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Ferencvaros</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>MTK Budapest</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>6</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>374</v>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="R10" t="n">
+        <v>200</v>
+      </c>
+      <c r="S10" t="n">
+        <v>40</v>
+      </c>
+      <c r="T10" t="n">
+        <v>38.2</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Italian Serie A</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Lecce x Juventus</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Lecce</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Juventus</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Lay Home/DC X2 (FavVis &lt;= 1.65)</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>2645</v>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="R11" t="n">
+        <v>200</v>
+      </c>
+      <c r="S11" t="n">
+        <v>31.25</v>
+      </c>
+      <c r="T11" t="n">
+        <v>29.84</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Portuguese Primeira Liga</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>CD Nacional Funchal x Braga</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>CD Nacional Funchal</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Braga</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lay Home/DC X2 (FavVis &lt;= 1.65)</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>2972</v>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="R12" t="n">
+        <v>200</v>
+      </c>
+      <c r="S12" t="n">
+        <v>31.25</v>
+      </c>
+      <c r="T12" t="n">
+        <v>29.84</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Israeli Premier League</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Hapoel Petach Tikva x Beitar Jerusalem</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Hapoel Petach Tikva</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Beitar Jerusalem</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>260</v>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="R13" t="n">
+        <v>200</v>
+      </c>
+      <c r="S13" t="n">
+        <v>38.46</v>
+      </c>
+      <c r="T13" t="n">
+        <v>36.73</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Belgian Pro League</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Union St Gilloise x Cercle Brugge</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Union St Gilloise</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Cercle Brugge</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>2015</v>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="R14" t="n">
+        <v>200</v>
+      </c>
+      <c r="S14" t="n">
+        <v>38.46</v>
+      </c>
+      <c r="T14" t="n">
+        <v>36.73</v>
       </c>
     </row>
   </sheetData>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-25.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-25.xlsx
@@ -1180,15 +1180,19 @@
       <c r="K9" t="n">
         <v>1.48</v>
       </c>
-      <c r="L9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>1-3</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>✅ LIQUIDADO</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1262,15 +1266,19 @@
       <c r="K10" t="n">
         <v>1.37</v>
       </c>
-      <c r="L10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>AO Home Win</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>✅ LIQUIDADO</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1344,15 +1352,19 @@
       <c r="K11" t="n">
         <v>1.55</v>
       </c>
-      <c r="L11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>✅ LIQUIDADO</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1426,15 +1438,19 @@
       <c r="K12" t="n">
         <v>1.56</v>
       </c>
-      <c r="L12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>RED</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>✅ LIQUIDADO</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1508,15 +1524,19 @@
       <c r="K13" t="n">
         <v>1.36</v>
       </c>
-      <c r="L13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>✅ LIQUIDADO</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1590,15 +1610,19 @@
       <c r="K14" t="n">
         <v>1.35</v>
       </c>
-      <c r="L14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>AO Home Win</t>
+        </is>
+      </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>✅ LIQUIDADO</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-25.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T14"/>
+  <dimension ref="A1:P20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,26 +509,6 @@
           <t>Liquidez_Lay</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>Hora_Str</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>Risco_Red_R$</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Stake_Sugerida_R$</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>Lucro_Green_R$</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -538,32 +518,32 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Italian Serie A</t>
+          <t>Portuguese Segunda Liga</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Inter x Fiorentina</t>
+          <t>AVS Futebol SAD x Tondela</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Inter</t>
+          <t>AVS Futebol SAD</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Tondela</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lay Draw (Fav &lt;= 1.40)</t>
+          <t>Lay 0x3 Top 3 (Aprovado)</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
@@ -573,10 +553,10 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>6.2</v>
+        <v>22</v>
       </c>
       <c r="K2" t="n">
-        <v>1.39</v>
+        <v>1.88</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -599,21 +579,7 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>15907</v>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="R2" t="n">
-        <v>200</v>
-      </c>
-      <c r="S2" t="n">
-        <v>38.46</v>
-      </c>
-      <c r="T2" t="n">
-        <v>36.73</v>
+        <v>353</v>
       </c>
     </row>
     <row r="3">
@@ -624,32 +590,32 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Danish Superliga</t>
+          <t>Italian Serie A</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Silkeborg x FC Nordsjaelland</t>
+          <t>Inter x Fiorentina</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Inter</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>FC Nordsjaelland</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lay Home/DC X2 (FavVis &lt;= 1.65)</t>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
@@ -659,14 +625,14 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="K3" t="n">
-        <v>1.62</v>
+        <v>1.39</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -685,21 +651,7 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>725</v>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="R3" t="n">
-        <v>200</v>
-      </c>
-      <c r="S3" t="n">
-        <v>41.67</v>
-      </c>
-      <c r="T3" t="n">
-        <v>39.79</v>
+        <v>15907</v>
       </c>
     </row>
     <row r="4">
@@ -710,32 +662,32 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Czech 1 Liga</t>
+          <t>Danish Superliga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Sparta Prague x Slovacko</t>
+          <t>Silkeborg x FC Nordsjaelland</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sparta Prague</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Slovacko</t>
+          <t>FC Nordsjaelland</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lay Draw (Fav &lt;= 1.40)</t>
+          <t>Lay Home/DC X2 (FavVis &lt;= 1.65)</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
@@ -745,14 +697,14 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>6.8</v>
+        <v>5.8</v>
       </c>
       <c r="K4" t="n">
-        <v>1.31</v>
+        <v>1.62</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>AO Home Win</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -771,21 +723,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1031</v>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="R4" t="n">
-        <v>200</v>
-      </c>
-      <c r="S4" t="n">
-        <v>34.48</v>
-      </c>
-      <c r="T4" t="n">
-        <v>32.93</v>
+        <v>725</v>
       </c>
     </row>
     <row r="5">
@@ -796,32 +734,32 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Belgian Pro League</t>
+          <t>Italian Serie A</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Club Brugge x Sint Truiden</t>
+          <t>Genoa x Venezia</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sint Truiden</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lay Draw (Fav &lt;= 1.40)</t>
+          <t>Lay 2x2 Top 3 (Aprovado)</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
@@ -831,14 +769,14 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>6.8</v>
+        <v>16</v>
       </c>
       <c r="K5" t="n">
-        <v>1.31</v>
+        <v>2.28</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>3-2</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -857,21 +795,7 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>304</v>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="R5" t="n">
-        <v>200</v>
-      </c>
-      <c r="S5" t="n">
-        <v>34.48</v>
-      </c>
-      <c r="T5" t="n">
-        <v>32.93</v>
+        <v>240</v>
       </c>
     </row>
     <row r="6">
@@ -882,32 +806,32 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Swedish Allsvenskan</t>
+          <t>Czech 1 Liga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Mjallby x Hammarby</t>
+          <t>Sparta Prague x Slovacko</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mjallby</t>
+          <t>Sparta Prague</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Slovacko</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lay Home/DC X2 (FavVis &lt;= 1.65)</t>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
@@ -917,14 +841,14 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>8</v>
+        <v>6.8</v>
       </c>
       <c r="K6" t="n">
-        <v>1.46</v>
+        <v>1.31</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0-2</t>
+          <t>AO Home Win</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -943,21 +867,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1108</v>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="R6" t="n">
-        <v>200</v>
-      </c>
-      <c r="S6" t="n">
-        <v>28.57</v>
-      </c>
-      <c r="T6" t="n">
-        <v>27.28</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="7">
@@ -968,32 +878,32 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Dutch Eredivisie</t>
+          <t>Belgian Pro League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam x Ajax</t>
+          <t>Club Brugge x Sint Truiden</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Sint Truiden</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lay Home/DC X2 (FavVis &lt;= 1.65)</t>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
@@ -1003,14 +913,14 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="K7" t="n">
-        <v>1.55</v>
+        <v>1.31</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>3-2</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1029,21 +939,7 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1559</v>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>12:45</t>
-        </is>
-      </c>
-      <c r="R7" t="n">
-        <v>200</v>
-      </c>
-      <c r="S7" t="n">
-        <v>38.46</v>
-      </c>
-      <c r="T7" t="n">
-        <v>36.73</v>
+        <v>304</v>
       </c>
     </row>
     <row r="8">
@@ -1054,32 +950,32 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Greek Super League</t>
+          <t>Spanish La Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NFC Volos x Panathinaikos</t>
+          <t>Celta Vigo x Betis</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>NFC Volos</t>
+          <t>Celta Vigo</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Betis</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lay Draw (Fav &lt;= 1.40)</t>
+          <t>Lay 2x2 Top 3 (Aprovado)</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
@@ -1089,14 +985,14 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>6.4</v>
+        <v>16</v>
       </c>
       <c r="K8" t="n">
-        <v>1.32</v>
+        <v>2.82</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>0-0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1115,21 +1011,7 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>2398</v>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="R8" t="n">
-        <v>200</v>
-      </c>
-      <c r="S8" t="n">
-        <v>37.04</v>
-      </c>
-      <c r="T8" t="n">
-        <v>35.37</v>
+        <v>1955</v>
       </c>
     </row>
     <row r="9">
@@ -1140,27 +1022,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>German Bundesliga</t>
+          <t>Swedish Allsvenskan</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Freiburg x Bayern Munich</t>
+          <t>Mjallby x Hammarby</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Mjallby</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bayern Munich</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1175,14 +1057,14 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="K9" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>1-3</t>
+          <t>0-2</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1201,21 +1083,7 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>3957</v>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
-      <c r="R9" t="n">
-        <v>200</v>
-      </c>
-      <c r="S9" t="n">
-        <v>34.48</v>
-      </c>
-      <c r="T9" t="n">
-        <v>32.93</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="10">
@@ -1226,32 +1094,32 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Hungarian NB I</t>
+          <t>Dutch Eredivisie</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Ferencvaros x MTK Budapest</t>
+          <t>Sparta Rotterdam x Ajax</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ferencvaros</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>MTK Budapest</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lay Draw (Fav &lt;= 1.40)</t>
+          <t>Lay 2x2 Top 3 (Aprovado)</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
@@ -1261,14 +1129,14 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="K10" t="n">
-        <v>1.37</v>
+        <v>1.55</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>AO Home Win</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1287,21 +1155,7 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>374</v>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="R10" t="n">
-        <v>200</v>
-      </c>
-      <c r="S10" t="n">
-        <v>40</v>
-      </c>
-      <c r="T10" t="n">
-        <v>38.2</v>
+        <v>380</v>
       </c>
     </row>
     <row r="11">
@@ -1312,27 +1166,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Italian Serie A</t>
+          <t>Dutch Eredivisie</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Lecce x Juventus</t>
+          <t>Sparta Rotterdam x Ajax</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1347,14 +1201,14 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>7.4</v>
+        <v>6.2</v>
       </c>
       <c r="K11" t="n">
         <v>1.55</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0-2</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1373,21 +1227,7 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>2645</v>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="R11" t="n">
-        <v>200</v>
-      </c>
-      <c r="S11" t="n">
-        <v>31.25</v>
-      </c>
-      <c r="T11" t="n">
-        <v>29.84</v>
+        <v>1559</v>
       </c>
     </row>
     <row r="12">
@@ -1398,32 +1238,32 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Portuguese Primeira Liga</t>
+          <t>Greek Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>CD Nacional Funchal x Braga</t>
+          <t>NFC Volos x Panathinaikos</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CD Nacional Funchal</t>
+          <t>NFC Volos</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Braga</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lay Home/DC X2 (FavVis &lt;= 1.65)</t>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
@@ -1433,19 +1273,19 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>7.4</v>
+        <v>6.4</v>
       </c>
       <c r="K12" t="n">
-        <v>1.56</v>
+        <v>1.32</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>RED</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1459,21 +1299,7 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>2972</v>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="R12" t="n">
-        <v>200</v>
-      </c>
-      <c r="S12" t="n">
-        <v>31.25</v>
-      </c>
-      <c r="T12" t="n">
-        <v>29.84</v>
+        <v>2398</v>
       </c>
     </row>
     <row r="13">
@@ -1484,32 +1310,32 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Israeli Premier League</t>
+          <t>German Bundesliga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Hapoel Petach Tikva x Beitar Jerusalem</t>
+          <t>Freiburg x Bayern Munich</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Hapoel Petach Tikva</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Bayern Munich</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lay Draw (Fav &lt;= 1.40)</t>
+          <t>Lay Home/DC X2 (FavVis &lt;= 1.65)</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
@@ -1519,14 +1345,14 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="K13" t="n">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>1-3</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1545,21 +1371,7 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>260</v>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>15:15</t>
-        </is>
-      </c>
-      <c r="R13" t="n">
-        <v>200</v>
-      </c>
-      <c r="S13" t="n">
-        <v>38.46</v>
-      </c>
-      <c r="T13" t="n">
-        <v>36.73</v>
+        <v>3957</v>
       </c>
     </row>
     <row r="14">
@@ -1570,27 +1382,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Belgian Pro League</t>
+          <t>Hungarian NB I</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Union St Gilloise x Cercle Brugge</t>
+          <t>Ferencvaros x MTK Budapest</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Union St Gilloise</t>
+          <t>Ferencvaros</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>MTK Budapest</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1605,47 +1417,461 @@
         </is>
       </c>
       <c r="J14" t="n">
+        <v>6</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>AO Home Win</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>✅ LIQUIDADO</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Italian Serie A</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Lecce x Juventus</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Lecce</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Juventus</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Lay Home/DC X2 (FavVis &lt;= 1.65)</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>✅ LIQUIDADO</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>2645</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Portuguese Primeira Liga</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>CD Nacional Funchal x Braga</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>CD Nacional Funchal</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Braga</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Lay Home/DC X2 (FavVis &lt;= 1.65)</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>✅ LIQUIDADO</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>2972</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Israeli Premier League</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Hapoel Petach Tikva x Beitar Jerusalem</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Hapoel Petach Tikva</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Beitar Jerusalem</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
         <v>6.2</v>
       </c>
-      <c r="K14" t="n">
+      <c r="K17" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>✅ LIQUIDADO</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Belgian Pro League</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Union St Gilloise x Cercle Brugge</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Union St Gilloise</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Cercle Brugge</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="K18" t="n">
         <v>1.35</v>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>AO Home Win</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>GREEN</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>✅ LIQUIDADO</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="O18" t="inlineStr">
         <is>
           <t>coletor (KO-10)</t>
         </is>
       </c>
-      <c r="P14" t="n">
+      <c r="P18" t="n">
         <v>2015</v>
       </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>15:15</t>
-        </is>
-      </c>
-      <c r="R14" t="n">
-        <v>200</v>
-      </c>
-      <c r="S14" t="n">
-        <v>38.46</v>
-      </c>
-      <c r="T14" t="n">
-        <v>36.73</v>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Italian Serie A</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Udinese x AC Milan</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Udinese</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>AC Milan</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Lay 0x3 Top 3 (Aprovado)</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>21</v>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>✅ LIQUIDADO</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>1017</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Argentinian Primera Nacional</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Club Atletico Mitre x Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Club Atletico Mitre</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Lay 0x3 Top 3 (Aprovado)</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>21</v>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>0-3</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>✅ LIQUIDADO</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>310</v>
       </c>
     </row>
   </sheetData>
